--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -11,6 +11,7 @@
     <sheet name="sequence" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="operands" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="support_fc" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="support_fc_logic" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1189,8 +1190,6 @@
           <t>Comando motore uscita</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1208,8 +1207,6 @@
           <t>Allarme sovratemperatura</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1227,8 +1224,6 @@
           <t>Comando start da HMI</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1246,8 +1241,6 @@
           <t>Memoria ausiliaria ciclo</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1265,8 +1258,6 @@
           <t>Segnale supporto transizioni</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1284,8 +1275,6 @@
           <t>Modo manuale attivo</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1332,6 +1321,159 @@
         <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>Rete_1_Condizioni</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>result_member</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>condition_expression</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>condition_operands</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>network_index</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>network_title</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>io</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RUN_ENABLE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>I_START_BTN AND NOT I_STOP_BTN</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>I_START_BTN;I_STOP_BTN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Rete start/stop</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Q_MOTOR_CMD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RUN_ENABLE AND SAFETY_OK</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RUN_ENABLE;SAFETY_OK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Comando motore</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COND_LINEA_OK</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SENS_A OR SENS_B</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SENS_A;SENS_B</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Logica rete 1</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Rete_1_Condizioni</t>
         </is>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -1103,7 +1103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1129,16 +1129,6 @@
           <t>comment</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>network_index</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>network_title</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1273,56 +1263,6 @@
       <c r="C9" t="inlineStr">
         <is>
           <t>Modo manuale attivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>COND_LINEA_OK</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Support network 1</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Rete_1_Condizioni</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>OUT_LINEA_CMD</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Support network 1 output</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Rete_1_Condizioni</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1377,12 +1317,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>network_index</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>network_title</t>
+          <t>network</t>
         </is>
       </c>
     </row>
@@ -1412,8 +1347,6 @@
           <t>Rete start/stop</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1439,43 +1372,6 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>Comando motore</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>COND_LINEA_OK</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SENS_A OR SENS_B</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SENS_A;SENS_B</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Logica rete 1</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Rete_1_Condizioni</t>
         </is>
       </c>
     </row>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -1103,15 +1103,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1143,7 +1136,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pulsante start da IO</t>
+          <t>Pulsante start</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1153,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pulsante stop da IO</t>
+          <t>Pulsante stop</t>
         </is>
       </c>
     </row>
@@ -1177,92 +1170,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Comando motore uscita</t>
+          <t>Comando motore</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>diag</t>
+          <t>aux</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALM_OVERTEMP</t>
+          <t>M_CYCLE_ACTIVE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allarme sovratemperatura</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>hmi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HMI_CMD_START</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Comando start da HMI</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>aux</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>M_CYCLE_ACTIVE</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Memoria ausiliaria ciclo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>transitions</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>T_INTERLOCK_OK</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Segnale supporto transizioni</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>mode</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MODE_MANUAL_ACTIVE</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Modo manuale attivo</t>
+          <t>Memoria ciclo</t>
         </is>
       </c>
     </row>
@@ -1279,15 +1204,6 @@
   </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1347,6 +1263,9 @@
           <t>Rete start/stop</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1373,6 +1292,9 @@
         <is>
           <t>Comando motore</t>
         </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -11,7 +11,6 @@
     <sheet name="sequence" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="operands" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="support_fc" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="support_fc_logic" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1103,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,7 +1118,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>result_member</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>condition_expression</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>condition_operands</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>network</t>
         </is>
       </c>
     </row>
@@ -1134,11 +1153,15 @@
           <t>I_START_BTN</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Pulsante start</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1151,149 +1174,79 @@
           <t>I_STOP_BTN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Pulsante stop</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Q_MOTOR_CMD</t>
-        </is>
-      </c>
+          <t>io</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Comando motore</t>
-        </is>
+          <t>RUN_ENABLE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>I_START_BTN AND NOT I_STOP_BTN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>I_START_BTN;I_STOP_BTN</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rete start/stop</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aux</t>
+          <t>output</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M_CYCLE_ACTIVE</t>
+          <t>Q_MOTOR_CMD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Memoria ciclo</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>result_member</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>condition_expression</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>condition_operands</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>io</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>RUN_ENABLE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>I_START_BTN AND NOT I_STOP_BTN</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>I_START_BTN;I_STOP_BTN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Rete start/stop</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
           <t>Q_MOTOR_CMD</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>RUN_ENABLE AND SAFETY_OK</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>RUN_ENABLE;SAFETY_OK</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Comando motore</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,11 +525,6 @@
       <c r="I1" t="inlineStr">
         <is>
           <t>parallel_group</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>jump_labels_used</t>
         </is>
       </c>
     </row>
@@ -844,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,25 +855,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>write_action</t>
+          <t>timer_instruction_kind</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>timer_instruction_kind</t>
+          <t>timer_preset_value</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>timer_preset_value</t>
+          <t>trigger_operands</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>trigger_operands</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -895,11 +885,6 @@
           <t>aux</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Consenso avvio</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -912,11 +897,6 @@
           <t>aux</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ramo parallelo A</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -929,11 +909,6 @@
           <t>aux</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Ramo parallelo B</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -946,11 +921,6 @@
           <t>alarm</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Allarme temperatura</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -963,11 +933,6 @@
           <t>hmi</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Comando HMI</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -985,11 +950,6 @@
           <t>=</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Uscita motore</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1017,11 +977,6 @@
           <t>M_OK_A</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Timer fase</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1034,11 +989,6 @@
           <t>external</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Ingresso esterno</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1051,11 +1001,6 @@
           <t>manual_mode</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Rete manuale</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1068,11 +1013,6 @@
           <t>auto_mode</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Rete automatica</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1083,11 +1023,6 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>aux</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Fine ciclo</t>
         </is>
       </c>
     </row>
@@ -1153,15 +1088,11 @@
           <t>I_START_BTN</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Pulsante start</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1174,15 +1105,11 @@
           <t>I_STOP_BTN</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Pulsante stop</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1190,7 +1117,6 @@
           <t>io</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>RUN_ENABLE</t>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,20 +855,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>datatype</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>timer_instruction_kind</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>timer_preset_value</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>trigger_operands</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -945,7 +950,7 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>=</t>
         </is>
@@ -962,17 +967,17 @@
           <t>timer</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>S5T#3S</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>M_OK_A</t>
         </is>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -890,6 +890,11 @@
           <t>aux</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -902,6 +907,11 @@
           <t>aux</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -914,6 +924,11 @@
           <t>aux</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -926,6 +941,11 @@
           <t>alarm</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -938,6 +958,11 @@
           <t>hmi</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -950,6 +975,11 @@
           <t>output</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>=</t>
@@ -967,6 +997,11 @@
           <t>timer</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>IEC_TIMER</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>SD</t>
@@ -994,6 +1029,11 @@
           <t>external</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1006,6 +1046,11 @@
           <t>manual_mode</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1018,6 +1063,11 @@
           <t>auto_mode</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bool</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1028,6 +1078,11 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>aux</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Bool</t>
         </is>
       </c>
     </row>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,11 +870,6 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>trigger_operands</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
           <t>note</t>
         </is>
       </c>
@@ -980,11 +975,6 @@
           <t>Bool</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1002,19 +992,19 @@
           <t>IEC_TIMER</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>t_on</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>3s</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S5T#3S</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>M_OK_A</t>
+          <t>preset timer esempio</t>
         </is>
       </c>
     </row>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -839,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -860,12 +860,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>timer_instruction_kind</t>
+          <t>control_kind</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>timer_preset_value</t>
+          <t>control_value</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -1073,6 +1073,38 @@
       <c r="C12" t="inlineStr">
         <is>
           <t>Bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>counter</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>IEC_COUNTER</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ctu</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>contatore esempio</t>
         </is>
       </c>
     </row>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,15 +451,10 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>operands_used_in_condition</t>
+          <t>flow_type</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>flow_type</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>parallel_group</t>
         </is>
@@ -496,11 +491,6 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>M_START</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
           <t>alternative</t>
         </is>
       </c>
@@ -536,15 +526,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>M_OK_A</t>
+          <t>parallel</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
-        <is>
-          <t>parallel</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -581,15 +566,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>M_OK_B</t>
+          <t>parallel</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
-        <is>
-          <t>parallel</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -626,15 +606,10 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M_END_A</t>
+          <t>parallel</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
-        <is>
-          <t>parallel</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -671,15 +646,10 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>M_END_B</t>
+          <t>parallel</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
-        <is>
-          <t>parallel</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
@@ -716,11 +686,6 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>M_DONE</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
           <t>alternative</t>
         </is>
       </c>
@@ -755,11 +720,6 @@
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>M_RESET</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>alternative</t>
         </is>
@@ -1230,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,15 +1216,10 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>condition_operands</t>
+          <t>comment</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>network</t>
         </is>
@@ -1281,7 +1236,7 @@
           <t>I_START_BTN</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Pulsante start</t>
         </is>
@@ -1298,7 +1253,7 @@
           <t>I_STOP_BTN</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Pulsante stop</t>
         </is>
@@ -1322,15 +1277,10 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I_START_BTN;I_STOP_BTN</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>Rete start/stop</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="F4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1357,15 +1307,10 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RUN_ENABLE;SAFETY_OK</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
           <t>Comando motore</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="F5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1387,15 +1332,10 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>F5;F6;F7;F8;Timer_OK</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
           <t>Esempio precedenza con parentesi</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="F6" t="n">
         <v>2</v>
       </c>
     </row>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -1190,7 +1190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1216,10 +1216,15 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>coil_mode</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>network</t>
         </is>
@@ -1236,7 +1241,7 @@
           <t>I_START_BTN</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Pulsante start</t>
         </is>
@@ -1253,7 +1258,7 @@
           <t>I_STOP_BTN</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Pulsante stop</t>
         </is>
@@ -1275,12 +1280,12 @@
           <t>I_START_BTN AND NOT I_STOP_BTN</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Rete start/stop</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1305,12 +1310,12 @@
           <t>RUN_ENABLE AND SAFETY_OK</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Comando motore</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1330,12 +1335,12 @@
           <t>(F5 OR (NOT F6 AND F7)) AND (F8 AND Timer_OK)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Esempio precedenza con parentesi</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>2</v>
       </c>
     </row>

--- a/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
+++ b/docs/templates/ir_excel_template_single_page_with_support_fc.xlsx
@@ -431,12 +431,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>from_step</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>transition_id</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>from_step</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -471,12 +471,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>T1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>S1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,12 +506,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>T2</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>S2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>T3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>S2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>T4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>S3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -626,12 +626,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>T5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>S4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>T6</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>S5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>T7</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>S6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
